--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26867-2025 artfynd.xlsx
+++ b/artfynd/A 26867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814959</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126814958</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
